--- a/Result/checksun_type/文化用紙.xlsx
+++ b/Result/checksun_type/文化用紙.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>34.27</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>30752.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>26021.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>26021.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>27135.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>14215.12</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>14215.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>1676.657039741152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>30752</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>30752.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.19</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>32.61</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>32.61</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>15599.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>23408.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>23408.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>25268.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14319.64</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14319.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1114.689186374952</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>15599</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>15599.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>33.77</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.07</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>9517.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>24723.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>24723.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>24634.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>14301.02</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>14301.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>1895.603353481278</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>9517</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>9517.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>33.68</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>31971.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>27396.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>27396</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24460.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14465.96</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>14465.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>3595.137758151694</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>31971</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>31971.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>33.58</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>31.91</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>42270.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>26727.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>26727.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>22014.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14159.48</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>14159.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>3488.860559175446</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>42270</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>42270.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>17685.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>28248.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>28248.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>18790.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>13569.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>13569.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>2108.9695406674</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>17685</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>17685.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.92999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22175.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>27128.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>27128.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>17701.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>13365.52</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>13365.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2696.4834592035</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22175</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22175.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>32.44</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>32.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>22879.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>24545.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>24545.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>16522.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>13109.9</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>13109.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2958.414647854945</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22879</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22879.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>31.82</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>28629.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>21524.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>21524.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>15788.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>12943.64</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>12943.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>3151.51582279076</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>28629</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>28629.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>31.32999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>32.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>49876.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>17301.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>17301</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>13897.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12734.7</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12734.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2698.74907902797</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>49876</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>49876.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>30.82</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>32.8</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>12082.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9331.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9331.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>10294.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>11920.4</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>11920.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-320.9087363127292</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>12082</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>12082.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15398999.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>34221878.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>34221878.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>36617575.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>25241855.24</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>25241855.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>2053470.207403455</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15398999</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15398999.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>27.15</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>31549272.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>38918740.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>38918740.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>36738077.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>25462351.56</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>25462351.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>4244409.746218462</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>31549272</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>31549272.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.79</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.79</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>66917706.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>44512832.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>44512832.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>34620079.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>25398329.14</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>25398329.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>5492350.917874958</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>66917706</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>66917706.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>38460831.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>40957668.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>40957668.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>29797516.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>24401116.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>24401116.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>3289493.558888707</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>38460831</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>38460831.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>18782585.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>40170944.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>40170944.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>26760865.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>24094528.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>24094528.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>3074023.454662319</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>18782585</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>18782585.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>38883310.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>39013271.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>39013271.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>27803305.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>23943921.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>23943921.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>4764805.968100969</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>38883310</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>38883310.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>59519729.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>34557413.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>34557413.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>25421344.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>23374106.74</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>23374106.74</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4856388.809866868</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>59519729</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>59519729.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>25.59</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>49141889.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24727325.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24727325.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>20699524.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>22332782.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>22332782.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2602734.090608615</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>49141889</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>49141889.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>34527209.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>18637363.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>18637363.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>17271105.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>21698630.5</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>21698630.5</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>402183.988432236</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>34527209</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>34527209.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>12994221.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13350786.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13350786.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>15342192.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>21347314.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>21347314.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1189964.157120883</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>12994221</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>12994221.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>25.92000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16604021.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>16593340.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>16593340</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>16535240.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>21345209.82</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>21345209.82</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1114856.930871021</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16604021</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16604021.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>11.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12.15</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>18005548.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>19177580.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>19177580.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>29580981.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>22421239.98</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>22421239.98</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1785117.168213371</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>18005548</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>18005548.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,21 +10947,17 @@
           <t>11.71</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM25" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AO25" t="inlineStr">
         <is>
           <t>12.17</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>12.17</t>
-        </is>
-      </c>
       <c r="AP25" t="inlineStr">
         <is>
           <t>-186.05</t>
@@ -11140,20 +10998,16 @@
           <t>7727015.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>21268995.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>21268995.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>30374102.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22678426.12</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22678426.12</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1555011.203350872</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7727015</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7727015.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,21 +11377,17 @@
           <t>11.74</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AM26" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>12.18</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
       <c r="AP26" t="inlineStr">
         <is>
           <t>-383.32</t>
@@ -11576,20 +11428,16 @@
           <t>18977250.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>27449635.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>27449635.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>30912071.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>23124120.4</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>23124120.4</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-69480.88914190978</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>18977250</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>18977250.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>20356352.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>32034183.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>32034183.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>30173949.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>23085176.4</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>23085176.4</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>849804.4129116759</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>20356352</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>20356352.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>12.18</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>30821738.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>41658482.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>41658482.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>29511896.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>23187205.66</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>23187205.66</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1984958.043955665</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>30821738</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>30821738.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>12.35</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>28462621.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>39984381.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>39984381.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>27721210.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>22822287.78</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>22822287.78</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>2414423.37244866</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>28462621</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>28462621.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>12.52</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>38630216.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>39479209.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>39479209</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>26345598.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>22740925.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>22740925</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>3194478.399851203</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>38630216</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>38630216.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>12.54</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>41899989.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>34374507.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>34374507.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>25719252.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>22198404.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>22198404</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>3105369.03186015</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>41899989</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>41899989.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>68477848.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>28313716.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>28313716.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>23284004.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21757255.78</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21757255.78</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2516831.076449357</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>68477848</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>68477848.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>22451234.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>17365310.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>17365310</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>18118301.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>20655784.36</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>20655784.36</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1261452.005439252</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>22451234</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>22451234.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>25936758.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>15458039.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>15458039.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>18385630.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>20507029.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>20507029.94</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1682524.479371578</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>25936758</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>25936758.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>17.64</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>6791803.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>10058420.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>10058420.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>20353292.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>15094194.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>15094194.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1996695.871977523</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6791803</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6791803.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17.63</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>5688835.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>12748490.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>12748490.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>23731866.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>15360881.76</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>15360881.76</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1408807.419375379</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5688835</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5688835.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>17.99</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>16688578.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>15079634.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>15079634.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>25532824.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>15494092.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>15494092</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-400477.0792517662</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>16688578</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>16688578.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>11811096.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>17474774.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>17474774.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>25895143.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>15509598.64</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>15509598.64</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-124246.3048161827</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>11811096</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>11811096.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>9311790.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>28417473.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>28417473</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>26672932.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>15411366.58</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>15411366.58</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>797393.8124066554</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>9311790</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>9311790.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>18.33</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>20242154.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>30648164.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>30648164.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>26970051.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>15411161.88</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>15411161.88</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>2353326.986567616</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>20242154</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>20242154.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>18.4</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>17344555.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>34715241.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>34715241.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>26279480.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>15172436.36</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>15172436.36</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>3320930.842991576</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>17344555</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>17344555.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>18.37</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>28664279.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>35986014.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>35986014.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>26734953.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>14965321.98</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>14965321.98</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>4895074.429204676</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>28664279</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>28664279.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>18.17</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.6</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>66524587.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>34315511.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>34315511.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>25013118.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>14532416.86</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>14532416.86</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>5756199.32275179</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>66524587</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>66524587.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>20465247.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>24928391.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>24928391.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>19851734.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>13542466.52</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>13542466.52</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>2724337.623435102</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>20465247</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>20465247.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>40577540.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>23291937.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>23291937.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>18777885.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>13347392.76</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>13347392.76</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>3230738.137860011</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>40577540</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>40577540.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
